--- a/results/pooled_results_OR_multi_exposure_models_cold_mother_excludes_rheumatism.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_cold_mother_excludes_rheumatism.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1637E08B-F456-4D86-A3C2-65232E24C7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5A4263-59B4-4663-B8DA-7F63A6BB475B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{B34C9846-5C9E-4699-A4E5-B319E9F77E52}"/>
   </bookViews>
@@ -325,6 +325,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -340,9 +343,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -750,33 +750,33 @@
     <row r="6" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
       <c r="H6"/>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="19"/>
       <c r="M6"/>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="16"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="19"/>
       <c r="R6"/>
-      <c r="S6" s="14" t="s">
+      <c r="S6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="16"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="19"/>
     </row>
     <row r="8" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
@@ -845,34 +845,34 @@
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="17"/>
+      <c r="E9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="20"/>
       <c r="H9"/>
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="17"/>
+      <c r="J9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="20"/>
       <c r="M9"/>
       <c r="N9" s="1">
         <v>1</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="17"/>
+      <c r="O9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="20"/>
       <c r="R9"/>
       <c r="S9" s="1">
         <v>1</v>
       </c>
-      <c r="T9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="U9" s="17"/>
+      <c r="T9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="20"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
@@ -948,10 +948,10 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="13"/>
+      <c r="E12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="16"/>
       <c r="H12"/>
       <c r="M12"/>
       <c r="R12"/>
@@ -1077,10 +1077,10 @@
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="13"/>
+      <c r="J17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="16"/>
       <c r="L17"/>
       <c r="M17"/>
       <c r="R17"/>
@@ -1154,10 +1154,10 @@
       <c r="N21" s="1">
         <v>1</v>
       </c>
-      <c r="O21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="13"/>
+      <c r="O21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="16"/>
       <c r="R21"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
@@ -1196,16 +1196,16 @@
       <c r="K23"/>
       <c r="L23"/>
       <c r="M23"/>
-      <c r="N23" s="1">
+      <c r="N23" s="9">
         <v>2.1218699000000001</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="9">
         <v>1.0107944</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="9">
         <v>4.4542510000000002</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="10">
         <v>4.6780000000000002E-2</v>
       </c>
       <c r="R23"/>
@@ -1263,10 +1263,10 @@
       <c r="S26" s="1">
         <v>1</v>
       </c>
-      <c r="T26" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U26" s="13"/>
+      <c r="T26" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="16"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="5"/>
@@ -1504,34 +1504,34 @@
       <c r="D35" s="1">
         <v>1</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="13"/>
+      <c r="E35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="16"/>
       <c r="H35"/>
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="13"/>
+      <c r="J35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="16"/>
       <c r="M35"/>
       <c r="N35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="13"/>
+      <c r="O35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="16"/>
       <c r="R35"/>
       <c r="S35" s="1">
         <v>1</v>
       </c>
-      <c r="T35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U35" s="13"/>
+      <c r="T35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U35" s="16"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
@@ -1664,34 +1664,34 @@
       <c r="D39" s="1">
         <v>1</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="13"/>
+      <c r="E39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="16"/>
       <c r="H39"/>
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="J39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K39" s="13"/>
+      <c r="J39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K39" s="16"/>
       <c r="M39"/>
       <c r="N39" s="1">
         <v>1</v>
       </c>
-      <c r="O39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P39" s="13"/>
+      <c r="O39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P39" s="16"/>
       <c r="R39"/>
       <c r="S39" s="1">
         <v>1</v>
       </c>
-      <c r="T39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U39" s="13"/>
+      <c r="T39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U39" s="16"/>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="5"/>
@@ -1767,34 +1767,34 @@
       <c r="D42" s="1">
         <v>1</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="13"/>
+      <c r="E42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="16"/>
       <c r="H42"/>
       <c r="I42" s="1">
         <v>1</v>
       </c>
-      <c r="J42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="13"/>
+      <c r="J42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K42" s="16"/>
       <c r="M42"/>
       <c r="N42" s="1">
         <v>1</v>
       </c>
-      <c r="O42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="13"/>
+      <c r="O42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P42" s="16"/>
       <c r="R42"/>
       <c r="S42" s="1">
         <v>1</v>
       </c>
-      <c r="T42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="13"/>
+      <c r="T42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="16"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B43" s="5"/>
@@ -1925,34 +1925,34 @@
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="13"/>
+      <c r="E46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="16"/>
       <c r="H46"/>
       <c r="I46" s="1">
         <v>1</v>
       </c>
-      <c r="J46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="13"/>
+      <c r="J46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="16"/>
       <c r="M46"/>
       <c r="N46" s="1">
         <v>1</v>
       </c>
-      <c r="O46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="13"/>
+      <c r="O46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="16"/>
       <c r="R46"/>
       <c r="S46" s="1">
         <v>1</v>
       </c>
-      <c r="T46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U46" s="13"/>
+      <c r="T46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="16"/>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B47" s="5"/>
@@ -2028,95 +2028,119 @@
       <c r="D49" s="1">
         <v>1</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="13"/>
+      <c r="E49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="16"/>
       <c r="H49"/>
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K49" s="13"/>
+      <c r="J49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="K49" s="16"/>
       <c r="M49"/>
       <c r="N49" s="1">
         <v>1</v>
       </c>
-      <c r="O49" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="13"/>
+      <c r="O49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="16"/>
       <c r="R49"/>
       <c r="S49" s="1">
         <v>1</v>
       </c>
-      <c r="T49" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="U49" s="13"/>
+      <c r="T49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U49" s="16"/>
     </row>
     <row r="50" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="6"/>
       <c r="C50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="13">
         <v>2.0367625</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="13">
         <v>0.96082190000000001</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="13">
         <v>4.3175550999999999</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="14">
         <v>6.3469999999999999E-2</v>
       </c>
-      <c r="H50" s="20"/>
-      <c r="I50" s="18">
+      <c r="H50" s="15"/>
+      <c r="I50" s="13">
         <v>2.1088152999999998</v>
       </c>
-      <c r="J50" s="18">
+      <c r="J50" s="13">
         <v>0.99638990000000005</v>
       </c>
-      <c r="K50" s="18">
+      <c r="K50" s="13">
         <v>4.4632148999999997</v>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="14">
         <v>5.1110000000000003E-2</v>
       </c>
-      <c r="M50" s="20"/>
-      <c r="N50" s="18">
+      <c r="M50" s="15"/>
+      <c r="N50" s="13">
         <v>2.0306831000000001</v>
       </c>
-      <c r="O50" s="18">
+      <c r="O50" s="13">
         <v>0.95720930000000004</v>
       </c>
-      <c r="P50" s="18">
+      <c r="P50" s="13">
         <v>4.3080170999999998</v>
       </c>
-      <c r="Q50" s="19">
+      <c r="Q50" s="14">
         <v>6.4869999999999997E-2</v>
       </c>
-      <c r="R50" s="20"/>
-      <c r="S50" s="18">
+      <c r="R50" s="15"/>
+      <c r="S50" s="13">
         <v>2.0859353</v>
       </c>
-      <c r="T50" s="18">
+      <c r="T50" s="13">
         <v>0.9845507</v>
       </c>
-      <c r="U50" s="18">
+      <c r="U50" s="13">
         <v>4.419403</v>
       </c>
-      <c r="V50" s="19">
+      <c r="V50" s="14">
         <v>5.4940000000000003E-2</v>
       </c>
     </row>
     <row r="51" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="T39:U39"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="O42:P42"/>
@@ -2125,30 +2149,6 @@
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="O46:P46"/>
     <mergeCell ref="T46:U46"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="S6:V6"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="T49:U49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
